--- a/payment_forms/043_child_support_payment_declaration_form--payment_forms.xlsx
+++ b/payment_forms/043_child_support_payment_declaration_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,8 +889,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,12 +918,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'cash_payment',_'value':_'cash'}</t>
+          <t>cash_payment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Cash Payment', 'value': 'cash'}</t>
+          <t>Cash Payment</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'personal_or_cashier_check',_'value':_'check'}</t>
+          <t>personal_or_cashier_check</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Personal or Cashier Check', 'value': 'check'}</t>
+          <t>Personal or Cashier Check</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer_(ach)',_'value':_'bank'}</t>
+          <t>bank_transfer_(ach)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Transfer (ACH)', 'value': 'bank'}</t>
+          <t>Bank Transfer (ACH)</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'money_order',_'value':_'money_order'}</t>
+          <t>money_order</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Money Order', 'value': 'money_order'}</t>
+          <t>Money Order</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_confirmed',_'value':_true}</t>
+          <t>yes_-_confirmed</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Confirmed', 'value': True}</t>
+          <t>Yes - Confirmed</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_partial_payment',_'value':_false}</t>
+          <t>no_-_partial_payment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'No - Partial Payment', 'value': False}</t>
+          <t>No - Partial Payment</t>
         </is>
       </c>
     </row>
